--- a/game-stats/Week1_PAK-LIONS_vs_Warriors.xlsx
+++ b/game-stats/Week1_PAK-LIONS_vs_Warriors.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>QB1</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>NATE ARE</t>
+          <t>Nate Are</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>GABE ARE</t>
+          <t>Gabe Are</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>HAMEED O</t>
+          <t>Hameed O</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>Ed</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>KUNLE A.</t>
+          <t>Kunle A.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>JOSIAH LANDO</t>
+          <t>Josiah Lando</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>LEITH L.</t>
+          <t>Leith L.</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>FASIAL ISHAQUE</t>
+          <t>Fasial Ishaque</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ROHAIL CHOHAN</t>
+          <t>Rohail Chohan</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>BRANDON MOORE</t>
+          <t>Brandon Moore</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>EFFONY SCALES</t>
+          <t>Effony Scales</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>SAHEED LAWAL</t>
+          <t>Saheed Lawal</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>MARZELL WELLS</t>
+          <t>Marzell Wells</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>JOSH INYANG</t>
+          <t>Josh Inyang</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>MYSHAWN ROLLINS</t>
+          <t>Myshawn Rollins</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>FREDO</t>
+          <t>Fredo</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>MARI KNIGHT</t>
+          <t>Mari Knight</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>NAJEE S.</t>
+          <t>Najee S.</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>DAVID OWUSU</t>
+          <t>David Owusu</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>GENIUS</t>
+          <t>Genius</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>T'Auhndre Winters</t>
+          <t>T'Auhrdre Winters</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
